--- a/data/trans_orig/P19C01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C01-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137967</t>
+          <t>139478</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182834</t>
+          <t>183055</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>188763</t>
+          <t>188178</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>241256</t>
+          <t>240525</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>336201</t>
+          <t>344985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>409817</t>
+          <t>410961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>506531</t>
+          <t>506310</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>551398</t>
+          <t>549887</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>717703</t>
+          <t>718434</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>770196</t>
+          <t>770781</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1238507</t>
+          <t>1237363</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1312123</t>
+          <t>1303339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,07%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>356551</t>
+          <t>357515</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>424081</t>
+          <t>423722</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>449688</t>
+          <t>450667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>518810</t>
+          <t>522558</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>827123</t>
+          <t>827857</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>923958</t>
+          <t>925693</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>890367</t>
+          <t>890726</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>957897</t>
+          <t>956933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>853454</t>
+          <t>849706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>922576</t>
+          <t>921597</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1762754</t>
+          <t>1761019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1859589</t>
+          <t>1858855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>162390</t>
+          <t>161404</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203397</t>
+          <t>203994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140539</t>
+          <t>140654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>181311</t>
+          <t>180364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>313150</t>
+          <t>314785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>370840</t>
+          <t>372892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>249035</t>
+          <t>248438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>290042</t>
+          <t>291028</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227472</t>
+          <t>228419</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>268244</t>
+          <t>268129</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>490375</t>
+          <t>488323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>548065</t>
+          <t>546430</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,45%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>692031</t>
+          <t>687407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>776288</t>
+          <t>777003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>813224</t>
+          <t>813931</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>914498</t>
+          <t>907265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1528215</t>
+          <t>1525596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1660205</t>
+          <t>1658507</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1679957</t>
+          <t>1679242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1764214</t>
+          <t>1768838</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1825508</t>
+          <t>1832741</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1926782</t>
+          <t>1926075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3536047</t>
+          <t>3537745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3668037</t>
+          <t>3670656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114583</t>
+          <t>116191</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>159724</t>
+          <t>156497</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>232499</t>
+          <t>234081</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>291643</t>
+          <t>291333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>361260</t>
+          <t>360586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>433400</t>
+          <t>433220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>619450</t>
+          <t>622677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>664591</t>
+          <t>662983</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>836570</t>
+          <t>836880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>895714</t>
+          <t>894132</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1473986</t>
+          <t>1474166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1546126</t>
+          <t>1546800</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,1%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>493464</t>
+          <t>490396</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>567900</t>
+          <t>570058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>547037</t>
+          <t>543547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>626605</t>
+          <t>625251</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1059526</t>
+          <t>1064522</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1171164</t>
+          <t>1171170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1120378</t>
+          <t>1118220</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1194814</t>
+          <t>1197882</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>962675</t>
+          <t>964029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1042243</t>
+          <t>1045733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2106394</t>
+          <t>2106388</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2218032</t>
+          <t>2213036</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167548</t>
+          <t>169609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>211067</t>
+          <t>214395</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>209633</t>
+          <t>210148</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>253208</t>
+          <t>253337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>392027</t>
+          <t>388743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>452897</t>
+          <t>452391</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,25%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>231067</t>
+          <t>227739</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>274586</t>
+          <t>272525</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170515</t>
+          <t>170386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>214090</t>
+          <t>213575</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>412960</t>
+          <t>413466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>473830</t>
+          <t>477114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>808037</t>
+          <t>805411</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>909703</t>
+          <t>907108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1023478</t>
+          <t>1023924</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1134161</t>
+          <t>1133320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1862630</t>
+          <t>1865070</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2006694</t>
+          <t>2008171</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1999883</t>
+          <t>2002478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2101549</t>
+          <t>2104175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2007055</t>
+          <t>2007896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2117738</t>
+          <t>2117292</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4044107</t>
+          <t>4042630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4188171</t>
+          <t>4185731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>107215</t>
+          <t>108328</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144699</t>
+          <t>145202</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>194057</t>
+          <t>189584</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>240928</t>
+          <t>242415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>311288</t>
+          <t>312412</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>376512</t>
+          <t>376734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>312720</t>
+          <t>312217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>350204</t>
+          <t>349091</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>397946</t>
+          <t>396459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>444817</t>
+          <t>449290</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>719781</t>
+          <t>719559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>785005</t>
+          <t>783881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,5%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>663724</t>
+          <t>667214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>743423</t>
+          <t>748902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>714942</t>
+          <t>720362</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>803975</t>
+          <t>801725</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1404764</t>
+          <t>1411232</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1524022</t>
+          <t>1521800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>953182</t>
+          <t>947703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1032881</t>
+          <t>1029391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>904744</t>
+          <t>906994</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>993777</t>
+          <t>988357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1881302</t>
+          <t>1883524</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2000560</t>
+          <t>1994092</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,56%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>228234</t>
+          <t>228325</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>272946</t>
+          <t>275015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>240249</t>
+          <t>240228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>286297</t>
+          <t>285744</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>484183</t>
+          <t>482891</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>548873</t>
+          <t>548577</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>226298</t>
+          <t>224229</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271010</t>
+          <t>270919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222023</t>
+          <t>222576</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>268071</t>
+          <t>268092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>458691</t>
+          <t>458987</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>523381</t>
+          <t>524673</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,07%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1027788</t>
+          <t>1026277</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1129720</t>
+          <t>1126684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1187554</t>
+          <t>1183916</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1294915</t>
+          <t>1293182</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2244466</t>
+          <t>2249900</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2397900</t>
+          <t>2391987</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1523549</t>
+          <t>1526585</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1625481</t>
+          <t>1626992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1560998</t>
+          <t>1562731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1668359</t>
+          <t>1671997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3111282</t>
+          <t>3117195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3264716</t>
+          <t>3259282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2023 (tasa de respuesta: 99,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>162959</t>
+          <t>160943</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>202222</t>
+          <t>201668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>276692</t>
+          <t>277240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>318299</t>
+          <t>317702</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>449581</t>
+          <t>445745</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>504873</t>
+          <t>506029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282219</t>
+          <t>282773</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>321482</t>
+          <t>323498</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>403317</t>
+          <t>403914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>444924</t>
+          <t>444376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>701184</t>
+          <t>700028</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>756476</t>
+          <t>760312</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>63,04%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>809027</t>
+          <t>857760</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1337705</t>
+          <t>1334330</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>961360</t>
+          <t>887290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1423827</t>
+          <t>1414366</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1968663</t>
+          <t>1920650</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2704690</t>
+          <t>2694421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>892832</t>
+          <t>896207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1421510</t>
+          <t>1372777</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>774079</t>
+          <t>783540</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1236546</t>
+          <t>1310616</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1723752</t>
+          <t>1734021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2459779</t>
+          <t>2507792</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>56,63%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>409318</t>
+          <t>411209</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>460100</t>
+          <t>457038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>417362</t>
+          <t>420018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>460098</t>
+          <t>462002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>838533</t>
+          <t>841283</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>906322</t>
+          <t>909713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>171920</t>
+          <t>174982</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222702</t>
+          <t>220811</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>191513</t>
+          <t>189609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>234249</t>
+          <t>231593</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>377310</t>
+          <t>373919</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>445099</t>
+          <t>442349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1361013</t>
+          <t>1308733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1944285</t>
+          <t>1947985</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1646578</t>
+          <t>1555447</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2145808</t>
+          <t>2143540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3279152</t>
+          <t>3311067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4043381</t>
+          <t>4022774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1402713</t>
+          <t>1399013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1985985</t>
+          <t>2038265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1425325</t>
+          <t>1427593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1924555</t>
+          <t>2015686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2874750</t>
+          <t>2895357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3638979</t>
+          <t>3607064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C01-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139478</t>
+          <t>139134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183055</t>
+          <t>182302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>188178</t>
+          <t>189792</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>240525</t>
+          <t>239323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>344985</t>
+          <t>343062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>410961</t>
+          <t>414915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>506310</t>
+          <t>507063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>549887</t>
+          <t>550231</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>718434</t>
+          <t>719636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>770781</t>
+          <t>769167</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1237363</t>
+          <t>1233409</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1303339</t>
+          <t>1305262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,19%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>357515</t>
+          <t>354626</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>423722</t>
+          <t>423785</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>450667</t>
+          <t>451968</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>522558</t>
+          <t>522823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>827857</t>
+          <t>827020</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>925693</t>
+          <t>931053</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>890726</t>
+          <t>890663</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>956933</t>
+          <t>959822</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>849706</t>
+          <t>849441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>921597</t>
+          <t>920296</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1761019</t>
+          <t>1755659</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1858855</t>
+          <t>1859692</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161404</t>
+          <t>160750</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203994</t>
+          <t>203772</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140654</t>
+          <t>139259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180364</t>
+          <t>178191</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>314785</t>
+          <t>314199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>372892</t>
+          <t>375727</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>248438</t>
+          <t>248660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291028</t>
+          <t>291682</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>228419</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>268129</t>
+          <t>269524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>488323</t>
+          <t>485488</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>546430</t>
+          <t>547016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,52%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>687407</t>
+          <t>687219</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>777003</t>
+          <t>780082</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>813931</t>
+          <t>812786</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>907265</t>
+          <t>908419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1525596</t>
+          <t>1521653</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1658507</t>
+          <t>1660640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1679242</t>
+          <t>1676163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1768838</t>
+          <t>1769026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1832741</t>
+          <t>1831587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1926075</t>
+          <t>1927220</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3537745</t>
+          <t>3535612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3670656</t>
+          <t>3674599</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,72%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116191</t>
+          <t>114705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>156497</t>
+          <t>157522</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>234081</t>
+          <t>232920</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>291333</t>
+          <t>289094</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>360586</t>
+          <t>361788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>433220</t>
+          <t>430979</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>622677</t>
+          <t>621652</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>662983</t>
+          <t>664469</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>836880</t>
+          <t>839119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>894132</t>
+          <t>895293</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1474166</t>
+          <t>1476407</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1546800</t>
+          <t>1545598</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>490396</t>
+          <t>491775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>570058</t>
+          <t>568978</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>543547</t>
+          <t>547713</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>625251</t>
+          <t>623967</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1064522</t>
+          <t>1056842</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1171170</t>
+          <t>1168176</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1118220</t>
+          <t>1119300</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1197882</t>
+          <t>1196503</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>964029</t>
+          <t>965313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1045733</t>
+          <t>1041567</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2106388</t>
+          <t>2109382</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2213036</t>
+          <t>2220716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,76%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169609</t>
+          <t>167362</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>214395</t>
+          <t>212452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210148</t>
+          <t>210285</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>253337</t>
+          <t>252123</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>388743</t>
+          <t>391616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>452391</t>
+          <t>454525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,49%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>227739</t>
+          <t>229682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>272525</t>
+          <t>274772</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170386</t>
+          <t>171600</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>213575</t>
+          <t>213438</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>413466</t>
+          <t>411332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>477114</t>
+          <t>474241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,77%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>805411</t>
+          <t>811625</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>907108</t>
+          <t>912132</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1023924</t>
+          <t>1024573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1133320</t>
+          <t>1127810</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1865070</t>
+          <t>1857134</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2008171</t>
+          <t>2006864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2002478</t>
+          <t>1997454</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2104175</t>
+          <t>2097961</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2007896</t>
+          <t>2013406</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2117292</t>
+          <t>2116643</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4042630</t>
+          <t>4043937</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4185731</t>
+          <t>4193667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108328</t>
+          <t>106984</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145202</t>
+          <t>143077</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>189584</t>
+          <t>192019</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>242415</t>
+          <t>240425</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>312412</t>
+          <t>313682</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>376734</t>
+          <t>370652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>312217</t>
+          <t>314342</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>349091</t>
+          <t>350435</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>396459</t>
+          <t>398449</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>449290</t>
+          <t>446855</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>719559</t>
+          <t>725641</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>783881</t>
+          <t>782611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,39%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>667214</t>
+          <t>666342</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>748902</t>
+          <t>748258</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>720362</t>
+          <t>718867</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>801725</t>
+          <t>801303</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1411232</t>
+          <t>1402281</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1521800</t>
+          <t>1523107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,73%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>947703</t>
+          <t>948347</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1029391</t>
+          <t>1030263</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>906994</t>
+          <t>907416</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>988357</t>
+          <t>989852</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1883524</t>
+          <t>1882217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1994092</t>
+          <t>2003043</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,82%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>228325</t>
+          <t>227968</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>275015</t>
+          <t>276020</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>240228</t>
+          <t>241185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>285744</t>
+          <t>287295</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>482891</t>
+          <t>484042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>548577</t>
+          <t>549393</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>224229</t>
+          <t>223224</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>270919</t>
+          <t>271276</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222576</t>
+          <t>221025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>268092</t>
+          <t>267135</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>458987</t>
+          <t>458171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>524673</t>
+          <t>523522</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,96%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1026277</t>
+          <t>1033083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1126684</t>
+          <t>1136496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1183916</t>
+          <t>1186049</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1293182</t>
+          <t>1290855</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2249900</t>
+          <t>2250137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2391987</t>
+          <t>2398730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1526585</t>
+          <t>1516773</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1626992</t>
+          <t>1620186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1562731</t>
+          <t>1565058</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1671997</t>
+          <t>1669864</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3117195</t>
+          <t>3110452</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3259282</t>
+          <t>3259045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>180962</t>
+          <t>196823</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>160943</t>
+          <t>177966</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>201668</t>
+          <t>222169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>296274</t>
+          <t>329892</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>277240</t>
+          <t>308809</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>317702</t>
+          <t>351415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>477235</t>
+          <t>526715</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>445745</t>
+          <t>494166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>506029</t>
+          <t>555231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>303479</t>
+          <t>340456</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282773</t>
+          <t>315110</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>323498</t>
+          <t>359313</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>425342</t>
+          <t>454700</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>403914</t>
+          <t>433177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>444376</t>
+          <t>475783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>728822</t>
+          <t>795156</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>700028</t>
+          <t>766640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>760312</t>
+          <t>827705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1170440</t>
+          <t>1253366</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>857760</t>
+          <t>1187355</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1334330</t>
+          <t>1300267</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1259033</t>
+          <t>1324501</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>887290</t>
+          <t>1284244</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1414366</t>
+          <t>1366564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2429473</t>
+          <t>2577868</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1920650</t>
+          <t>2510530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2694421</t>
+          <t>2644501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1060097</t>
+          <t>893112</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>896207</t>
+          <t>846211</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1372777</t>
+          <t>959123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>938873</t>
+          <t>786091</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>783540</t>
+          <t>744028</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1310616</t>
+          <t>826348</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1998969</t>
+          <t>1679202</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1734021</t>
+          <t>1612569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2507792</t>
+          <t>1746540</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>434804</t>
+          <t>482798</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>411209</t>
+          <t>453635</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>457038</t>
+          <t>509282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>439713</t>
+          <t>486508</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>420018</t>
+          <t>463650</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>462002</t>
+          <t>512653</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>874518</t>
+          <t>969306</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>841283</t>
+          <t>935370</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>909713</t>
+          <t>1008103</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>197216</t>
+          <t>219995</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174982</t>
+          <t>193511</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>220811</t>
+          <t>249158</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>211898</t>
+          <t>237905</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>189609</t>
+          <t>211760</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231593</t>
+          <t>260763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,27 +6406,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>409114</t>
+          <t>457900</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373919</t>
+          <t>419103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>442349</t>
+          <t>491836</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>632020</t>
+          <t>702793</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>632020</t>
+          <t>702793</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>632020</t>
+          <t>702793</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1283632</t>
+          <t>1427206</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1283632</t>
+          <t>1427206</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1283632</t>
+          <t>1427206</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1786205</t>
+          <t>1932988</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1308733</t>
+          <t>1871676</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1947985</t>
+          <t>1995317</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1995020</t>
+          <t>2140900</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1555447</t>
+          <t>2087989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2143540</t>
+          <t>2193378</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3781225</t>
+          <t>4073888</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3311067</t>
+          <t>3993304</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4022774</t>
+          <t>4155888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1560793</t>
+          <t>1453562</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1399013</t>
+          <t>1391233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2038265</t>
+          <t>1514874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1576113</t>
+          <t>1478697</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1427593</t>
+          <t>1426219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2015686</t>
+          <t>1531608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3136906</t>
+          <t>2932259</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2895357</t>
+          <t>2850259</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3607064</t>
+          <t>3012843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3346998</t>
+          <t>3386550</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3346998</t>
+          <t>3386550</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3346998</t>
+          <t>3386550</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6918131</t>
+          <t>7006147</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6918131</t>
+          <t>7006147</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6918131</t>
+          <t>7006147</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
